--- a/TT_Central_Gov_2026_Financing.xlsx
+++ b/TT_Central_Gov_2026_Financing.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Cen_GovTT_Financing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="TT_Gov_Borrowing" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -29,17 +29,19 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="00000000"/>
+      <color rgb="FF000000"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="13"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
@@ -51,8 +53,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F497D"/>
-        <bgColor rgb="001F497D"/>
+        <fgColor rgb="FF1F497D"/>
+        <bgColor rgb="FF1F497D"/>
       </patternFill>
     </fill>
   </fills>
@@ -76,7 +78,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -148,6 +150,218 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="12"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Central Government Gross Financing Architecture (TT$ Millions)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="stacked"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Cen_GovTT_Financing'!A5</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="2ECC71"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="2ECC71"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Cen_GovTT_Financing'!$B$1:$G$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Cen_GovTT_Financing'!$B$5:$G$5</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Cen_GovTT_Financing'!A9</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="2980B9"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="2980B9"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Cen_GovTT_Financing'!$B$1:$G$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Cen_GovTT_Financing'!$B$9:$G$9</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Cen_GovTT_Financing'!A4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="E67E22"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="E67E22"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Cen_GovTT_Financing'!$B$1:$G$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Cen_GovTT_Financing'!$B$4:$G$4</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <overlap val="100"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Financial Year Period</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Amount (TT$ Millions)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <numFmt formatCode="$#,###.0" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/chartsheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartsheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <drawing r:id="rId1"/>
+</chartsheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <absoluteAnchor>
+    <pos x="0" y="0"/>
+    <ext cx="0" cy="0"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </absoluteAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -440,19 +654,15 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="59" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="2" max="4"/>
+    <col width="21" customWidth="1" min="5" max="7"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr"/>
+    <row r="1" ht="17.4" customHeight="1">
+      <c r="A1" s="1" t="n"/>
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Oct '20/
@@ -574,8 +784,8 @@
       <c r="B5" s="4" t="n">
         <v>6040.6</v>
       </c>
-      <c r="C5" s="4" t="inlineStr"/>
-      <c r="D5" s="4" t="inlineStr"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
       <c r="E5" s="4" t="n">
         <v>2495.6</v>
       </c>
@@ -642,12 +852,12 @@
           <t>of which:</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr"/>
-      <c r="C8" s="4" t="inlineStr"/>
-      <c r="D8" s="4" t="inlineStr"/>
-      <c r="E8" s="4" t="inlineStr"/>
-      <c r="F8" s="4" t="inlineStr"/>
-      <c r="G8" s="4" t="inlineStr"/>
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="4" t="n"/>
+      <c r="D8" s="4" t="n"/>
+      <c r="E8" s="4" t="n"/>
+      <c r="F8" s="4" t="n"/>
+      <c r="G8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">

--- a/TT_Central_Gov_2026_Financing.xlsx
+++ b/TT_Central_Gov_2026_Financing.xlsx
@@ -1,52 +1,114 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Python-Projects\TT-Economic-Markers\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09B0D658-BC5A-445F-B075-0560D4E2979E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Cen_GovTT_Financing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="TT_Gov_Borrowing" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Cen_GovTT_Financing" sheetId="1" r:id="rId1"/>
+    <sheet name="TT_Gov_Borrowing" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
+  <si>
+    <t>Oct '20/
+Sep '21</t>
+  </si>
+  <si>
+    <t>Oct '21/
+Sep '22</t>
+  </si>
+  <si>
+    <t>Oct '22/
+Sep '23</t>
+  </si>
+  <si>
+    <t>Oct '23/
+Sep '24r</t>
+  </si>
+  <si>
+    <t>Oct '24/
+Sep '25r</t>
+  </si>
+  <si>
+    <t>Oct '25/
+Sep '26p</t>
+  </si>
+  <si>
+    <t>TOTAL FINANCING</t>
+  </si>
+  <si>
+    <t>NET EXTERNAL FINANCING</t>
+  </si>
+  <si>
+    <t>External Borrowings</t>
+  </si>
+  <si>
+    <t>Transfer from the Heritage and Stabilisation Fund (HSF)</t>
+  </si>
+  <si>
+    <t>Capital Repayments</t>
+  </si>
+  <si>
+    <t>NET DOMESTIC FINANCING</t>
+  </si>
+  <si>
+    <t>of which:</t>
+  </si>
+  <si>
+    <t>Domestic Borrowings</t>
+  </si>
+  <si>
+    <t>Other Financing</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,###.0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <color rgb="FF000000"/>
-      <sz val="11"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="13"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
       <name val="Calibri"/>
-      <b val="1"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -71,119 +133,85 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="12"/>
-  <chart>
-    <title>
-      <tx>
-        <rich>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="1"/>
+  <c:style val="12"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
           <a:bodyPr/>
+          <a:lstStyle/>
           <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr lang="en-TT"/>
               <a:t>Central Government Gross Financing Architecture (TT$ Millions)</a:t>
             </a:r>
           </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="stacked"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'Cen_GovTT_Financing'!A5</f>
-            </strRef>
-          </tx>
-          <spPr>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="1"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="7.9689297378670587E-2"/>
+          <c:y val="0.23912115003744086"/>
+          <c:w val="0.90416319134927992"/>
+          <c:h val="0.68544554608556219"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Cen_GovTT_Financing!$A$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Transfer from the Heritage and Stabilisation Fund (HSF)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
             <a:solidFill>
               <a:srgbClr val="2ECC71"/>
             </a:solidFill>
@@ -193,27 +221,97 @@
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Cen_GovTT_Financing'!$B$1:$G$1</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Cen_GovTT_Financing'!$B$5:$G$5</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <strRef>
-              <f>'Cen_GovTT_Financing'!A9</f>
-            </strRef>
-          </tx>
-          <spPr>
+          </c:spPr>
+          <c:invertIfNegative val="1"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Cen_GovTT_Financing!$B$1:$G$1</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Oct '20/
+Sep '21</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Oct '21/
+Sep '22</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Oct '22/
+Sep '23</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Oct '23/
+Sep '24r</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Oct '24/
+Sep '25r</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Oct '25/
+Sep '26p</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Cen_GovTT_Financing!$B$5:$G$5</c:f>
+              <c:numCache>
+                <c:formatCode>#,###.0</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>6040.6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2495.6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2775.7</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2565.1999999999998</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{6F2FDCE9-48DA-4B69-8628-5D25D57E5C99}">
+              <c14:invertSolidFillFmt>
+                <c14:spPr xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                  <a:ln>
+                    <a:solidFill>
+                      <a:srgbClr val="2ECC71"/>
+                    </a:solidFill>
+                    <a:prstDash val="solid"/>
+                  </a:ln>
+                </c14:spPr>
+              </c14:invertSolidFillFmt>
+            </c:ext>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-9BA9-4D53-9B38-A7824E061AF5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Cen_GovTT_Financing!$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Domestic Borrowings</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
             <a:solidFill>
               <a:srgbClr val="2980B9"/>
             </a:solidFill>
@@ -223,27 +321,103 @@
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Cen_GovTT_Financing'!$B$1:$G$1</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Cen_GovTT_Financing'!$B$9:$G$9</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="2"/>
-          <order val="2"/>
-          <tx>
-            <strRef>
-              <f>'Cen_GovTT_Financing'!A4</f>
-            </strRef>
-          </tx>
-          <spPr>
+          </c:spPr>
+          <c:invertIfNegative val="1"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Cen_GovTT_Financing!$B$1:$G$1</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Oct '20/
+Sep '21</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Oct '21/
+Sep '22</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Oct '22/
+Sep '23</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Oct '23/
+Sep '24r</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Oct '24/
+Sep '25r</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Oct '25/
+Sep '26p</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Cen_GovTT_Financing!$B$9:$G$9</c:f>
+              <c:numCache>
+                <c:formatCode>#,###.0</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>13471.4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5653.1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9793.1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8135.6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9435</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7754.1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{6F2FDCE9-48DA-4B69-8628-5D25D57E5C99}">
+              <c14:invertSolidFillFmt>
+                <c14:spPr xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                  <a:ln>
+                    <a:solidFill>
+                      <a:srgbClr val="2980B9"/>
+                    </a:solidFill>
+                    <a:prstDash val="solid"/>
+                  </a:ln>
+                </c14:spPr>
+              </c14:invertSolidFillFmt>
+            </c:ext>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-9BA9-4D53-9B38-A7824E061AF5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Cen_GovTT_Financing!$A$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>External Borrowings</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
             <a:solidFill>
               <a:srgbClr val="E67E22"/>
             </a:solidFill>
@@ -253,115 +427,248 @@
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Cen_GovTT_Financing'!$B$1:$G$1</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Cen_GovTT_Financing'!$B$4:$G$4</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <overlap val="100"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
+          </c:spPr>
+          <c:invertIfNegative val="1"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Cen_GovTT_Financing!$B$1:$G$1</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Oct '20/
+Sep '21</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Oct '21/
+Sep '22</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Oct '22/
+Sep '23</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Oct '23/
+Sep '24r</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Oct '24/
+Sep '25r</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Oct '25/
+Sep '26p</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Cen_GovTT_Financing!$B$4:$G$4</c:f>
+              <c:numCache>
+                <c:formatCode>#,###.0</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>291.39999999999998</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1685</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2601.8000000000002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8033.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1263.7</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>12135.7</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{6F2FDCE9-48DA-4B69-8628-5D25D57E5C99}">
+              <c14:invertSolidFillFmt>
+                <c14:spPr xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                  <a:ln>
+                    <a:solidFill>
+                      <a:srgbClr val="E67E22"/>
+                    </a:solidFill>
+                    <a:prstDash val="solid"/>
+                  </a:ln>
+                </c14:spPr>
+              </c14:invertSolidFillFmt>
+            </c:ext>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-9BA9-4D53-9B38-A7824E061AF5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="10"/>
+        <c:axId val="100"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="10"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
               <a:bodyPr/>
+              <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
+                  <a:rPr lang="en-TT"/>
                   <a:t>Financial Year Period</a:t>
                 </a:r>
               </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="0.46491655539486382"/>
+              <c:y val="0.87405399485154467"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="1"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="100"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="1"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="100"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:title>
+          <c:tx>
+            <c:rich>
               <a:bodyPr/>
+              <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
+                  <a:rPr lang="en-TT"/>
                   <a:t>Amount (TT$ Millions)</a:t>
                 </a:r>
               </a:p>
-            </rich>
-          </tx>
-        </title>
-        <numFmt formatCode="$#,###.0" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="9.1013245351551086E-2"/>
+              <c:y val="0.36947906923503804"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="1"/>
+        </c:title>
+        <c:numFmt formatCode="\$#,###.0" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="10"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="3.1199835219097569E-2"/>
+          <c:y val="3.7866670407828637E-2"/>
+          <c:w val="0.31996380275855435"/>
+          <c:h val="0.18322946560424044"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="1"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="1"/>
+  </c:chart>
+</c:chartSpace>
 </file>
 
 <file path=xl/chartsheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartsheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<chartsheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </chartsheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <absoluteAnchor>
-    <pos x="0" y="0"/>
-    <ext cx="0" cy="0"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="1" name="Chart 1"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="0" y="0"/>
+    <xdr:ext cx="8651488" cy="6272561"/>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </absoluteAnchor>
-</wsDr>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -648,290 +955,248 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col width="59" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="4"/>
-    <col width="21" customWidth="1" min="5" max="7"/>
+    <col min="1" max="1" width="59" customWidth="1"/>
+    <col min="2" max="4" width="20" customWidth="1"/>
+    <col min="5" max="7" width="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.4" customHeight="1">
-      <c r="A1" s="1" t="n"/>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Oct '20/
-Sep '21</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Oct '21/
-Sep '22</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Oct '22/
-Sep '23</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Oct '23/
-Sep '24r</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Oct '24/
-Sep '25r</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Oct '25/
-Sep '26p</t>
-        </is>
+    <row r="1" spans="1:7" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>TOTAL FINANCING</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="3">
         <v>12350.7</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="C2" s="3">
         <v>-1333</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" s="3">
         <v>3172.5</v>
       </c>
-      <c r="E2" s="3" t="n">
-        <v>9052.299999999999</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>10065.7</v>
-      </c>
-      <c r="G2" s="3" t="n">
+      <c r="E2" s="3">
+        <v>9052.2999999999993</v>
+      </c>
+      <c r="F2" s="3">
+        <v>10065.700000000001</v>
+      </c>
+      <c r="G2" s="3">
         <v>7000</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>NET EXTERNAL FINANCING</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="3">
         <v>5169.5</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>534.3</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>-138.7</v>
-      </c>
-      <c r="E3" s="3" t="n">
+      <c r="C3" s="3">
+        <v>534.29999999999995</v>
+      </c>
+      <c r="D3" s="3">
+        <v>-138.69999999999999</v>
+      </c>
+      <c r="E3" s="3">
         <v>7076.5</v>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="F3" s="3">
         <v>2690.8</v>
       </c>
-      <c r="G3" s="3" t="n">
+      <c r="G3" s="3">
         <v>6497.6</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>External Borrowings</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>291.4</v>
-      </c>
-      <c r="C4" s="4" t="n">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="4">
+        <v>291.39999999999998</v>
+      </c>
+      <c r="C4" s="4">
         <v>1685</v>
       </c>
-      <c r="D4" s="4" t="n">
-        <v>2601.8</v>
-      </c>
-      <c r="E4" s="4" t="n">
+      <c r="D4" s="4">
+        <v>2601.8000000000002</v>
+      </c>
+      <c r="E4" s="4">
         <v>8033.5</v>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="F4" s="4">
         <v>1263.7</v>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="G4" s="4">
         <v>12135.7</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Transfer from the Heritage and Stabilisation Fund (HSF)</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="4">
         <v>6040.6</v>
       </c>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="n">
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4">
         <v>2495.6</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="F5" s="4">
         <v>2775.7</v>
       </c>
-      <c r="G5" s="4" t="n">
-        <v>2565.2</v>
+      <c r="G5" s="4">
+        <v>2565.1999999999998</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Capital Repayments</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="4">
         <v>-1162.5</v>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="C6" s="4">
         <v>-1150.7</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" s="4">
         <v>-2740.5</v>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="E6" s="4">
         <v>-3452.6</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="F6" s="4">
         <v>-1348.6</v>
       </c>
-      <c r="G6" s="4" t="n">
-        <v>-8203.299999999999</v>
+      <c r="G6" s="4">
+        <v>-8203.2999999999993</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>NET DOMESTIC FINANCING</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="3">
         <v>7181.2</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="C7" s="3">
         <v>-1867.3</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" s="3">
         <v>3311.2</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" s="3">
         <v>1975.8</v>
       </c>
-      <c r="F7" s="3" t="n">
+      <c r="F7" s="3">
         <v>7374.9</v>
       </c>
-      <c r="G7" s="3" t="n">
+      <c r="G7" s="3">
         <v>502.4</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>of which:</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n"/>
-      <c r="C8" s="4" t="n"/>
-      <c r="D8" s="4" t="n"/>
-      <c r="E8" s="4" t="n"/>
-      <c r="F8" s="4" t="n"/>
-      <c r="G8" s="4" t="n"/>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Domestic Borrowings</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="4">
         <v>13471.4</v>
       </c>
-      <c r="C9" s="4" t="n">
+      <c r="C9" s="4">
         <v>5653.1</v>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D9" s="4">
         <v>9793.1</v>
       </c>
-      <c r="E9" s="4" t="n">
+      <c r="E9" s="4">
         <v>8135.6</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="F9" s="4">
         <v>9435</v>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="G9" s="4">
         <v>7754.1</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Capital Repayments</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="4">
         <v>-5733.5</v>
       </c>
-      <c r="C10" s="4" t="n">
+      <c r="C10" s="4">
         <v>-4397.5</v>
       </c>
-      <c r="D10" s="4" t="n">
-        <v>-8755.200000000001</v>
-      </c>
-      <c r="E10" s="4" t="n">
+      <c r="D10" s="4">
+        <v>-8755.2000000000007</v>
+      </c>
+      <c r="E10" s="4">
         <v>-3167.9</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="F10" s="4">
         <v>-5346.2</v>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="G10" s="4">
         <v>-7153.1</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Other Financing</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="n">
-        <v>-556.7</v>
-      </c>
-      <c r="C11" s="4" t="n">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="4">
+        <v>-556.70000000000005</v>
+      </c>
+      <c r="C11" s="4">
         <v>-3122.9</v>
       </c>
-      <c r="D11" s="4" t="n">
-        <v>2273.3</v>
-      </c>
-      <c r="E11" s="4" t="n">
+      <c r="D11" s="4">
+        <v>2273.3000000000002</v>
+      </c>
+      <c r="E11" s="4">
         <v>-2991.9</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="F11" s="4">
         <v>3286.1</v>
       </c>
-      <c r="G11" s="4" t="n">
-        <v>-98.59999999999999</v>
+      <c r="G11" s="4">
+        <v>-98.6</v>
       </c>
     </row>
   </sheetData>
